--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.99793315102795</v>
+        <v>8.287164137042042</v>
       </c>
       <c r="D2" t="n">
-        <v>50.78248406400513</v>
+        <v>8.252153660400834</v>
       </c>
       <c r="E2" t="n">
-        <v>14.37308095586117</v>
+        <v>2.33562565532744</v>
       </c>
       <c r="F2" t="n">
-        <v>14.3846585148081</v>
+        <v>2.337507008656316</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.51037530053579</v>
+        <v>6.745435986337067</v>
       </c>
       <c r="D3" t="n">
-        <v>41.73504707749143</v>
+        <v>6.781945150092358</v>
       </c>
       <c r="E3" t="n">
-        <v>14.37308095586117</v>
+        <v>2.33562565532744</v>
       </c>
       <c r="F3" t="n">
-        <v>14.3846585148081</v>
+        <v>2.337507008656316</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.12772212535181</v>
+        <v>4.245754845369669</v>
       </c>
       <c r="D4" t="n">
-        <v>25.8759326131446</v>
+        <v>4.204839049635997</v>
       </c>
       <c r="E4" t="n">
-        <v>14.37308095586117</v>
+        <v>2.33562565532744</v>
       </c>
       <c r="F4" t="n">
-        <v>14.3846585148081</v>
+        <v>2.337507008656316</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.29420566145034</v>
+        <v>5.247808419985681</v>
       </c>
       <c r="D5" t="n">
-        <v>32.52131281665964</v>
+        <v>5.284713332707192</v>
       </c>
       <c r="E5" t="n">
-        <v>14.37308095586117</v>
+        <v>2.33562565532744</v>
       </c>
       <c r="F5" t="n">
-        <v>14.3846585148081</v>
+        <v>2.337507008656316</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.41097607664138</v>
+        <v>5.266783612454224</v>
       </c>
       <c r="D6" t="n">
-        <v>32.11944503325812</v>
+        <v>5.219409817904445</v>
       </c>
       <c r="E6" t="n">
-        <v>14.37308095586117</v>
+        <v>2.33562565532744</v>
       </c>
       <c r="F6" t="n">
-        <v>14.3846585148081</v>
+        <v>2.337507008656316</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>4.499300285725593</v>
+        <v>0.7311362964304089</v>
       </c>
       <c r="D7" t="n">
-        <v>4.43948710708419</v>
+        <v>0.7214166549011809</v>
       </c>
       <c r="E7" t="n">
-        <v>14.37308095586117</v>
+        <v>2.33562565532744</v>
       </c>
       <c r="F7" t="n">
-        <v>14.3846585148081</v>
+        <v>2.337507008656316</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
